--- a/3_Component_Results/PRIVCON/Tables/naive_tbl/AVERAGE_1_9_qoq_forecast_error_table_first_eval.xlsx
+++ b/3_Component_Results/PRIVCON/Tables/naive_tbl/AVERAGE_1_9_qoq_forecast_error_table_first_eval.xlsx
@@ -447,22 +447,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.09181472831639451</v>
+        <v>0.09600817644943856</v>
       </c>
       <c r="C2">
-        <v>1.838119433117105</v>
+        <v>1.80873009846552</v>
       </c>
       <c r="D2">
-        <v>17.95916271619692</v>
+        <v>17.61564077771686</v>
       </c>
       <c r="E2">
-        <v>4.237825234267799</v>
+        <v>4.197099090766962</v>
       </c>
       <c r="F2">
-        <v>4.278989066040988</v>
+        <v>4.236938422049325</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>7.413020273047021E-05</v>
+        <v>0.01468009213018725</v>
       </c>
       <c r="C3">
-        <v>2.091730062774077</v>
+        <v>2.065323163278566</v>
       </c>
       <c r="D3">
-        <v>18.37008874755701</v>
+        <v>18.02077313488619</v>
       </c>
       <c r="E3">
-        <v>4.286034151468816</v>
+        <v>4.245088118624417</v>
       </c>
       <c r="F3">
-        <v>4.329548303496322</v>
+        <v>4.287303206256453</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.07697517700982162</v>
+        <v>0.08220551840041949</v>
       </c>
       <c r="C4">
-        <v>1.786816454232815</v>
+        <v>1.757849970078953</v>
       </c>
       <c r="D4">
-        <v>10.61989574786886</v>
+        <v>10.40978937293083</v>
       </c>
       <c r="E4">
-        <v>3.258818152009844</v>
+        <v>3.226420520163301</v>
       </c>
       <c r="F4">
-        <v>3.291670541969232</v>
+        <v>3.258118842759771</v>
       </c>
       <c r="G4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.005243764112333811</v>
+        <v>0.01623660523528441</v>
       </c>
       <c r="C5">
-        <v>1.747033754236641</v>
+        <v>1.722479860867259</v>
       </c>
       <c r="D5">
-        <v>11.76101659567932</v>
+        <v>11.52703298296657</v>
       </c>
       <c r="E5">
-        <v>3.429433859353365</v>
+        <v>3.395148447854168</v>
       </c>
       <c r="F5">
-        <v>3.465721123983597</v>
+        <v>3.430293046353186</v>
       </c>
       <c r="G5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.05952959428276366</v>
+        <v>0.05898005128837314</v>
       </c>
       <c r="C6">
-        <v>2.303747599184862</v>
+        <v>2.256443514421678</v>
       </c>
       <c r="D6">
-        <v>19.73205291551434</v>
+        <v>19.32099137610733</v>
       </c>
       <c r="E6">
-        <v>4.442077544968608</v>
+        <v>4.395564966657566</v>
       </c>
       <c r="F6">
-        <v>4.489698183225748</v>
+        <v>4.441680272014072</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.05422975282401672</v>
+        <v>0.04874314150827366</v>
       </c>
       <c r="C7">
-        <v>2.682531801186378</v>
+        <v>2.617845039322367</v>
       </c>
       <c r="D7">
-        <v>18.95522674257797</v>
+        <v>18.46984963255741</v>
       </c>
       <c r="E7">
-        <v>4.353760069477643</v>
+        <v>4.297656295302988</v>
       </c>
       <c r="F7">
-        <v>4.41186013140652</v>
+        <v>4.353557153608079</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.09175281835627994</v>
+        <v>0.1022826167921374</v>
       </c>
       <c r="C8">
-        <v>2.663306588085196</v>
+        <v>2.606163918896609</v>
       </c>
       <c r="D8">
-        <v>17.83211946726106</v>
+        <v>17.36922029732168</v>
       </c>
       <c r="E8">
-        <v>4.222809428243365</v>
+        <v>4.167639655407084</v>
       </c>
       <c r="F8">
-        <v>4.280047159788971</v>
+        <v>4.222311476013882</v>
       </c>
       <c r="G8">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -608,22 +608,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.07118176867328285</v>
+        <v>0.06729073421555903</v>
       </c>
       <c r="C9">
-        <v>3.846179246344002</v>
+        <v>3.663529280086617</v>
       </c>
       <c r="D9">
-        <v>30.36400025844973</v>
+        <v>28.9181007642355</v>
       </c>
       <c r="E9">
-        <v>5.51035391408299</v>
+        <v>5.377555277655033</v>
       </c>
       <c r="F9">
-        <v>5.653032108082237</v>
+        <v>5.509922990150629</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -631,22 +631,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.0002549338085925304</v>
+        <v>0.02184393926452912</v>
       </c>
       <c r="C10">
-        <v>4.420675973149636</v>
+        <v>4.12652061865264</v>
       </c>
       <c r="D10">
-        <v>37.99070145917987</v>
+        <v>35.28361613075038</v>
       </c>
       <c r="E10">
-        <v>6.163659745571609</v>
+        <v>5.940001357807116</v>
       </c>
       <c r="F10">
-        <v>6.415340456829838</v>
+        <v>6.164189045314939</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7">
